--- a/tour-deals-2026-0925-1011.xlsx
+++ b/tour-deals-2026-0925-1011.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9月25日-10月11日 團體旅遊比價'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'9月25日-10月11日 團體旅遊比價'!$A$1:$I$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,12 @@
       <b val="1"/>
       <color rgb="007F6000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +68,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,6 +95,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2073,82 +2084,82 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>理想旅遊</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>經典北越～雙龍灣・國賓號遊輪5天</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>越南 5天</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>NT$34,500</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>尚可報名</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>查看行程</t>
-        </is>
-      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>喜鴻假期</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>風華峴港5日（使用者 9/14 取消之訂單）</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>越南峴港 5日</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>NT$44,541</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>已取消報名（僅供價格參考）</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14 因操作錯誤取消，未付訂金；訂單總額 44,541</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>六</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>五福旅遊</t>
+          <t>理想旅遊</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>一口價</t>
+          <t>經典北越～雙龍灣・國賓號遊輪5天</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>泰國曼谷 6日</t>
+          <t>越南 5天</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NT$19,500起</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>已成團</t>
+          <t>NT$34,500</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>尚可報名</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2171,30 +2182,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>喜鴻假期</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>五福旅遊</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>一口價</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>韓國濟州 5日</t>
+          <t>泰國曼谷 6日</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>NT$11,999起</t>
+          <t>NT$19,500起</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>可售2・保證出團</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>9/30團已滿</t>
-        </is>
-      </c>
+          <t>已成團</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -2217,27 +2228,27 @@
           <t>喜鴻假期</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>酷航・迪士尼樂園・富士山</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>日本東京 5日</t>
+          <t>韓國濟州 5日</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NT$32,900起</t>
+          <t>NT$11,999起</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>可售10・已成團</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>可售2・保證出團</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9/30團已滿</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -2247,44 +2258,40 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>五福旅遊</t>
+          <t>喜鴻假期</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>（半自助）</t>
+          <t>酷航・迪士尼樂園・富士山</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>日本關西 5日</t>
+          <t>日本東京 5日</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>NT$22,999起</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>十人成行</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>半自助行程</t>
-        </is>
-      </c>
+          <t>NT$32,900起</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>可售10・已成團</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -2309,25 +2316,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>《不走人蔘保肝》易起遊濟州５日</t>
+          <t>（半自助）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>韓國濟州 5日</t>
+          <t>日本關西 5日</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NT$16,500起</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>已成團</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>NT$22,999起</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>十人成行</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>半自助行程</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -2352,17 +2363,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>法式情懷越南５日</t>
+          <t>《不走人蔘保肝》易起遊濟州５日</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>越南 5日</t>
+          <t>韓國濟州 5日</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>NT$30,900起</t>
+          <t>NT$16,500起</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2380,12 +2391,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2395,22 +2406,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>越捷越南富國島５日</t>
+          <t>法式情懷越南５日</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>越南富國島 5日</t>
+          <t>越南 5日</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NT$26,200起</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>尚可報名</t>
+          <t>NT$30,900起</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>已成團</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2423,12 +2434,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2438,29 +2449,25 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>峴港５日</t>
+          <t>越捷越南富國島５日</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>越南峴港 5日</t>
+          <t>越南富國島 5日</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>NT$29,900起</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>已成團</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>十人成行・星宇航空</t>
-        </is>
-      </c>
+          <t>NT$26,200起</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>尚可報名</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -2480,30 +2487,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>可樂旅遊</t>
+          <t>五福旅遊</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>連休首爾易起玩五日</t>
+          <t>峴港５日</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>韓國 5日</t>
+          <t>越南峴港 5日</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NT$18,900起</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>可點選出發日</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>NT$29,900起</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>已成團</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>十人成行・星宇航空</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -2513,12 +2524,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2528,17 +2539,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>連休瘋韓國四日（樂高樂園煙火秀）</t>
+          <t>連休首爾易起玩五日</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>韓國 4日</t>
+          <t>韓國 5日</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>NT$11,999起</t>
+          <t>NT$18,900起</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2571,7 +2582,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>連休瘋韓國四日（首爾樂園・星空圖書館）</t>
+          <t>連休瘋韓國四日（樂高樂園煙火秀）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2581,7 +2592,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NT$15,900起</t>
+          <t>NT$11,999起</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2609,23 +2620,27 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>喜鴻假期</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>可樂旅遊</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>連休瘋韓國四日（首爾樂園・星空圖書館）</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>韓國首爾 5日</t>
+          <t>韓國 4日</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>NT$29,900起</t>
+          <t>NT$15,900起</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>可售19</t>
+          <t>可點選出發日</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -2648,27 +2663,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>鳳凰旅遊</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>日本東北超值大滿貫５日（雙十連休・松島・銀山溫泉）</t>
-        </is>
-      </c>
+          <t>喜鴻假期</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>日本 5天</t>
+          <t>韓國首爾 5日</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NT$45,800</t>
+          <t>NT$29,900起</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>機位6・即將成團</t>
+          <t>可售19</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2681,40 +2692,40 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>五福旅遊</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>鳳凰旅遊</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>日本東北超值大滿貫５日（雙十連休・松島・銀山溫泉）</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>日本關西 5日</t>
+          <t>日本 5天</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>NT$22,999起</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>已成團</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>十人成行・雙十連假</t>
-        </is>
-      </c>
+          <t>NT$45,800</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>機位6・即將成團</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -2737,29 +2748,25 @@
           <t>五福旅遊</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>星宇富國島６日</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>越南富國島 6日</t>
+          <t>日本關西 5日</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NT$38,900起</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>尚可報名</t>
+          <t>NT$22,999起</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>已成團</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>星宇航空</t>
+          <t>十人成行・雙十連假</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -2781,32 +2788,32 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>可樂旅遊</t>
+          <t>五福旅遊</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>連休關西OMG五日（環球影城・哈利波特）</t>
+          <t>星宇富國島６日</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>日本關西 5日</t>
+          <t>越南富國島 6日</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>NT$37,888起</t>
+          <t>NT$38,900起</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>可點選出發日</t>
+          <t>尚可報名</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>雙十連假</t>
+          <t>星宇航空</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2833,7 +2840,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>連休瘋關西五日（環球影城・快速通關）</t>
+          <t>連休關西OMG五日（環球影城・哈利波特）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2843,7 +2850,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NT$45,800起</t>
+          <t>NT$37,888起</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2875,27 +2882,27 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>喜鴻假期</t>
+          <t>可樂旅遊</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>長榮航空</t>
+          <t>連休瘋關西五日（環球影城・快速通關）</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>泰國 6日</t>
+          <t>日本關西 5日</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>NT$19,988起</t>
+          <t>NT$45,800起</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>可售6</t>
+          <t>可點選出發日</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2927,27 +2934,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>美墨五城</t>
+          <t>長榮航空</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>美國 11日</t>
+          <t>泰國 6日</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NT$77,900起</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>保證出團・可售0（可候補）</t>
+          <t>NT$19,988起</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>可售6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>雙十連假・遊輪</t>
+          <t>雙十連假</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -2974,22 +2981,22 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>美加東賞楓</t>
+          <t>美墨五城</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>美國 12日</t>
+          <t>美國 11日</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>NT$196,900起</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>可售0（可候補）</t>
+          <t>NT$77,900起</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>保證出團・可售0（可候補）</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3006,40 +3013,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>六</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>五福旅遊</t>
+          <t>喜鴻假期</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>泰北南邦５日</t>
+          <t>美加東賞楓</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>泰國泰北 5日</t>
+          <t>美國 12日</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NT$30,800起</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>已成團</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>NT$196,900起</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>可售0（可候補）</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>雙十連假・遊輪</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>查看行程</t>
@@ -3059,23 +3070,27 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>喜鴻假期</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>五福旅遊</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>泰北南邦５日</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>泰國 5日</t>
+          <t>泰國泰北 5日</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>NT$24,888起</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>可售15</t>
+          <t>NT$30,800起</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>已成團</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3098,27 +3113,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>雄獅旅遊</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>馬來西亞5日遊｜大紅花渡假村、餵食鴕鳥（無購物）</t>
-        </is>
-      </c>
+          <t>喜鴻假期</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>馬來西亞 5日</t>
+          <t>泰國 5日</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NT$35,900起</t>
+          <t>NT$24,888起</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>詳見詳細頁</t>
+          <t>可售15</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3141,27 +3152,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>鳳凰旅遊</t>
+          <t>雄獅旅遊</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>(保出)紐航 依山傍水紐西蘭8號13天</t>
+          <t>馬來西亞5日遊｜大紅花渡假村、餵食鴕鳥（無購物）</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>紐西蘭 13天</t>
+          <t>馬來西亞 5日</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>NT$167,800</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>機位4・保證出團</t>
+          <t>NT$35,900起</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>詳見詳細頁</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3189,22 +3200,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(23優旅獎）東澳全覽~美夢成真9天(M/B)</t>
+          <t>(保出)紐航 依山傍水紐西蘭8號13天</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>澳洲 9天</t>
+          <t>紐西蘭 13天</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NT$113,900</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>機位5・報名</t>
+          <t>NT$167,800</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>機位4・保證出團</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -3217,12 +3228,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>六</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3232,22 +3243,22 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>曼谷芭塔雅・Pop Mart泡泡瑪特旗艦店5天</t>
+          <t>(23優旅獎）東澳全覽~美夢成真9天(M/B)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>泰國 5天</t>
+          <t>澳洲 9天</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>NT$24,300</t>
+          <t>NT$113,900</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>機位6・報名</t>
+          <t>機位5・報名</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3275,17 +3286,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>戀上檳城・升旗山生態公園・海邊五星度假酒店5天</t>
+          <t>曼谷芭塔雅・Pop Mart泡泡瑪特旗艦店5天</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>馬來西亞 5天</t>
+          <t>泰國 5天</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NT$36,300</t>
+          <t>NT$24,300</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3300,8 +3311,51 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>鳳凰旅遊</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>戀上檳城・升旗山生態公園・海邊五星度假酒店5天</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>馬來西亞 5天</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>NT$36,300</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>機位6・報名</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>查看行程</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I65"/>
+  <autoFilter ref="A1:I66"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
@@ -3339,34 +3393,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3408,7 +3462,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>黃色標示 = 已成團／保證出團</t>
+          <t>黃色標示 = 已成團／保證出團；灰色標示 = 使用者 9/14 取消的喜鴻「風華峴港5日」訂單，僅供價格參考（訂單總額 NT$44,541，未付訂金）</t>
         </is>
       </c>
     </row>

--- a/tour-deals-2026-0925-1011.xlsx
+++ b/tour-deals-2026-0925-1011.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,6 +97,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2121,10 +2122,14 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 因操作錯誤取消，未付訂金；訂單總額 44,541</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr"/>
+          <t>2026-09-14 因操作錯誤取消，未付訂金；訂單總額 44,541；目前 10/3 團 NT$35,900 起・保證出團・可候補</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>查看行程</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3393,34 +3398,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
